--- a/apollocam/ApolloCAM.xlsx
+++ b/apollocam/ApolloCAM.xlsx
@@ -1686,7 +1686,7 @@
     <row r="31" ht="18" customHeight="1">
       <c r="A31" s="34" t="inlineStr">
         <is>
-          <t>5. Admin password to unlock Loaders: ApolloAdmin2026</t>
+          <t>5. Admin password to unlock Loaders: see SETTINGS → ADMIN_PASSWORD</t>
         </is>
       </c>
       <c r="B31" s="35" t="n"/>
@@ -4232,7 +4232,7 @@
       </c>
       <c r="B13" s="34" t="inlineStr">
         <is>
-          <t>ApolloAdmin2026</t>
+          <t>ApolloCAM_ChangeMe!</t>
         </is>
       </c>
       <c r="C13" s="100" t="inlineStr">
